--- a/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_TD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08F61DDF-23AF-4602-AA5A-8EB762DAB595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46B49D2D-EE37-4D3E-B797-D68A93C5E089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="495" windowWidth="18900" windowHeight="11100" xr2:uid="{2EA24B31-36D3-473B-B750-FDCE0F3EC92A}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{253C0E5D-519A-431F-A904-93E59413E379}"/>
   </bookViews>
   <sheets>
     <sheet name="03_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C0F3820-7FE5-4C55-946E-CECBBD32240A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F776D7-BCC3-4B31-A0D2-8FBC97FBC038}">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46B49D2D-EE37-4D3E-B797-D68A93C5E089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A1FD54D-FF28-45DD-B501-FBE1D5F17DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{253C0E5D-519A-431F-A904-93E59413E379}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{1D981972-14A7-4063-8391-CA2682EC3928}"/>
   </bookViews>
   <sheets>
     <sheet name="03_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20F776D7-BCC3-4B31-A0D2-8FBC97FBC038}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC55C7-C02B-47AC-A665-37838BCE73DE}">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>25.04495</v>
+        <v>24.90662</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.4">
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>25.04495</v>
+        <v>24.90662</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.4">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>25.380929999999999</v>
+        <v>25.240770000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.4">
@@ -1073,7 +1073,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>25.67792</v>
+        <v>25.53754</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.4">
@@ -1087,7 +1087,7 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>23.57077</v>
+        <v>23.44267</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.4">
@@ -1101,7 +1101,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>22.01088</v>
+        <v>21.884530000000002</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.4">
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>22.53528</v>
+        <v>22.40232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.4">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>23.33098</v>
+        <v>23.193380000000001</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -1143,7 +1143,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>24.041630000000001</v>
+        <v>23.901520000000001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.4">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>24.623950000000001</v>
+        <v>24.481950000000001</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.4">
@@ -1171,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>25.13259</v>
+        <v>24.98922</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.4">
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>25.631879999999999</v>
+        <v>25.488379999999999</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.4">
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>26.128019999999999</v>
+        <v>25.984190000000002</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.4">
@@ -1213,7 +1213,7 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>26.35735</v>
+        <v>26.21472</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.4">
@@ -1227,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="D16">
-        <v>24.152470000000001</v>
+        <v>24.02298</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>22.50592</v>
+        <v>22.378679999999999</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.4">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>22.958580000000001</v>
+        <v>22.825019999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.4">
@@ -1269,7 +1269,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>23.695150000000002</v>
+        <v>23.557130000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>24.35783</v>
+        <v>24.217410000000001</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
@@ -1297,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>24.901589999999999</v>
+        <v>24.759350000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>25.379259999999999</v>
+        <v>25.235700000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>25.853560000000002</v>
+        <v>25.709910000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
@@ -1339,7 +1339,7 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>26.329329999999999</v>
+        <v>26.185359999999999</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.4">
@@ -1353,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>26.542090000000002</v>
+        <v>26.399329999999999</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.4">
@@ -1367,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="D26">
-        <v>24.323530000000002</v>
+        <v>24.193930000000002</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.4">
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>22.665859999999999</v>
+        <v>22.538509999999999</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>23.109159999999999</v>
+        <v>22.9755</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>23.837440000000001</v>
+        <v>23.69932</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
@@ -1423,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>24.492730000000002</v>
+        <v>24.352219999999999</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>25.029890000000002</v>
+        <v>24.88757</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.4">
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>25.501650000000001</v>
+        <v>25.35802</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.4">
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>25.970610000000001</v>
+        <v>25.826889999999999</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0A1FD54D-FF28-45DD-B501-FBE1D5F17DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B836EB2-2FBA-4927-A744-5232B6E0132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="18900" windowHeight="10965" xr2:uid="{1D981972-14A7-4063-8391-CA2682EC3928}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C9022D49-F194-48B0-B49D-9873873D9CF2}"/>
   </bookViews>
   <sheets>
     <sheet name="03_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CFC55C7-C02B-47AC-A665-37838BCE73DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3CAEBE-F5DE-4B11-A27F-A5A71C7D3C57}">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
+++ b/inputs/data_symbols_TD/03_LTAN06_800km_1213COLD_MZ_ALL_HEAT_MZ_0p5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hide\repository\thermal-deformation-optcomm\inputs\data_symbols_TD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8B836EB2-2FBA-4927-A744-5232B6E0132B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60935D49-FC16-47AF-86A8-68284CEBC1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C9022D49-F194-48B0-B49D-9873873D9CF2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{05421282-A18C-4B7E-969B-446D459E8B8E}"/>
   </bookViews>
   <sheets>
     <sheet name="03_LTAN06_800km_1213COLD_MZ_ALL" sheetId="1" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E3CAEBE-F5DE-4B11-A27F-A5A71C7D3C57}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E95C7D-2E49-4275-871E-E39927C9928B}">
   <dimension ref="A1:D33"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
